--- a/data/ВРП за 2000-2023.xlsx
+++ b/data/ВРП за 2000-2023.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\semen\Desktop\Новая диссертация\Данные\факторы\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\semen\PycharmProjects\Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B453FE-2081-4722-A48B-82785E7AEC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B653F4F6-B833-4E7C-93A4-BAB63794735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -78,9 +78,6 @@
     <t xml:space="preserve"> Ярославская область</t>
   </si>
   <si>
-    <t xml:space="preserve"> г.Москва</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Республика Карелия</t>
   </si>
   <si>
@@ -114,12 +111,6 @@
     <t xml:space="preserve"> Псковская область</t>
   </si>
   <si>
-    <t xml:space="preserve"> г.Санкт-Петербург</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Республика Адыгея (Адыгея)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Республика Калмыкия </t>
   </si>
   <si>
@@ -171,9 +162,6 @@
     <t xml:space="preserve"> Республика Мордовия</t>
   </si>
   <si>
-    <t xml:space="preserve"> Республика Татарстан (Татарстан)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Удмуртская Республика</t>
   </si>
   <si>
@@ -285,10 +273,22 @@
     <t>…</t>
   </si>
   <si>
-    <t>Чувашская Республика - Чувашия</t>
-  </si>
-  <si>
     <t>Кировская область</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Москва</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Санкт-Петербург</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Республика Татарстан</t>
+  </si>
+  <si>
+    <t>Чувашская Республика</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Республика Адыгея</t>
   </si>
 </sst>
 </file>
@@ -968,36 +968,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y88"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" customWidth="1"/>
-    <col min="4" max="4" width="33.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" customWidth="1"/>
-    <col min="8" max="8" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="27.7265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="3" max="3" width="27.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.7265625" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" customWidth="1"/>
+    <col min="6" max="6" width="23.54296875" customWidth="1"/>
+    <col min="7" max="7" width="22.1796875" customWidth="1"/>
+    <col min="8" max="8" width="24.453125" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" customWidth="1"/>
-    <col min="15" max="15" width="25.7109375" customWidth="1"/>
+    <col min="12" max="12" width="19.7265625" customWidth="1"/>
+    <col min="13" max="13" width="15.54296875" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" customWidth="1"/>
+    <col min="15" max="15" width="25.7265625" customWidth="1"/>
     <col min="16" max="16" width="39" customWidth="1"/>
-    <col min="17" max="17" width="27.5703125" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" customWidth="1"/>
-    <col min="19" max="19" width="28.140625" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" customWidth="1"/>
-    <col min="21" max="21" width="22.5703125" customWidth="1"/>
-    <col min="22" max="22" width="18.7109375" customWidth="1"/>
-    <col min="23" max="23" width="15.85546875" customWidth="1"/>
-    <col min="24" max="24" width="20.140625" customWidth="1"/>
-    <col min="25" max="25" width="18.5703125" customWidth="1"/>
+    <col min="17" max="17" width="27.54296875" customWidth="1"/>
+    <col min="18" max="18" width="19.54296875" customWidth="1"/>
+    <col min="19" max="19" width="28.1796875" customWidth="1"/>
+    <col min="20" max="20" width="14.453125" customWidth="1"/>
+    <col min="21" max="21" width="22.54296875" customWidth="1"/>
+    <col min="22" max="22" width="18.7265625" customWidth="1"/>
+    <col min="23" max="23" width="15.81640625" customWidth="1"/>
+    <col min="24" max="24" width="20.1796875" customWidth="1"/>
+    <col min="25" max="25" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B1" s="2">
         <v>2000</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>1341408.8999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>627017.80000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>893416.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>1494401.9</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>435227.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>792281.5</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>316018.2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>747687.1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>950272.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>9244579.5999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>398720.4</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>692685.4</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>556552.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>522646.8</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>750838.4</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>1149160.2</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
@@ -2380,9 +2380,9 @@
         <v>849769.9</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="B19" s="6">
         <v>1159034</v>
@@ -2457,9 +2457,9 @@
         <v>32339001.600000001</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="5">
         <v>28214.6</v>
@@ -2534,9 +2534,9 @@
         <v>434291.1</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="5">
         <v>59473.1</v>
@@ -2611,9 +2611,9 @@
         <v>1049365.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="5">
         <v>61806.9</v>
@@ -2688,9 +2688,9 @@
         <v>1263045.1000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="5">
         <v>11924</v>
@@ -2765,42 +2765,42 @@
         <v>501455.5</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="31" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M24" s="5">
         <v>273685.5</v>
@@ -2842,9 +2842,9 @@
         <v>761589.6</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="5">
         <v>69195.5</v>
@@ -2919,9 +2919,9 @@
         <v>1081822.8999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="5">
         <v>23290.3</v>
@@ -2996,9 +2996,9 @@
         <v>785205.9</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5">
         <v>56001.9</v>
@@ -3073,9 +3073,9 @@
         <v>1915187.7</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5">
         <v>55135</v>
@@ -3150,9 +3150,9 @@
         <v>1127497.3</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="5">
         <v>20965.5</v>
@@ -3227,9 +3227,9 @@
         <v>408968.1</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="5">
         <v>16178.9</v>
@@ -3304,9 +3304,9 @@
         <v>288750</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="B31" s="9">
         <v>188243</v>
@@ -3381,9 +3381,9 @@
         <v>10908028</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="B32" s="10">
         <v>5519.6</v>
@@ -3458,9 +3458,9 @@
         <v>223013</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B33" s="5">
         <v>6212.6</v>
@@ -3535,9 +3535,9 @@
         <v>166710.20000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -3584,9 +3584,9 @@
         <v>722497.8</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B35" s="5">
         <v>137125.29999999999</v>
@@ -3661,9 +3661,9 @@
         <v>4772036</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B36" s="5">
         <v>28115.7</v>
@@ -3738,9 +3738,9 @@
         <v>777718.3</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B37" s="5">
         <v>63767.1</v>
@@ -3815,9 +3815,9 @@
         <v>1384980.9</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B38" s="5">
         <v>88955</v>
@@ -3892,9 +3892,9 @@
         <v>2693193</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -3940,9 +3940,9 @@
         <v>253191.6</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B40" s="5">
         <v>20921.099999999999</v>
@@ -4017,9 +4017,9 @@
         <v>1034705.4</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B41" s="5">
         <v>2618.5</v>
@@ -4094,9 +4094,9 @@
         <v>95319.7</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="31" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5">
         <v>14081.3</v>
@@ -4171,9 +4171,9 @@
         <v>291100.40000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="31" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5">
         <v>5461.5</v>
@@ -4248,9 +4248,9 @@
         <v>143310.6</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="31" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5">
         <v>8363.2000000000007</v>
@@ -4325,24 +4325,24 @@
         <v>266555.8</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G45" s="5">
         <v>22898.9</v>
@@ -4402,9 +4402,9 @@
         <v>397223.4</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5">
         <v>53732.4</v>
@@ -4479,9 +4479,9 @@
         <v>1340782</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5">
         <v>145125</v>
@@ -4556,9 +4556,9 @@
         <v>2460269.4</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5">
         <v>11207.6</v>
@@ -4633,9 +4633,9 @@
         <v>304473.09999999998</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B49" s="5">
         <v>17553.400000000001</v>
@@ -4710,9 +4710,9 @@
         <v>396833</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="B50" s="5">
         <v>186154.4</v>
@@ -4787,9 +4787,9 @@
         <v>4583352.3</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5">
         <v>53307.4</v>
@@ -4864,7 +4864,7 @@
         <v>1102900.3</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>86</v>
       </c>
@@ -4941,9 +4941,9 @@
         <v>601316.69999999995</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B53" s="5">
         <v>124142.2</v>
@@ -5018,9 +5018,9 @@
         <v>2197280.1</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B54" s="5">
         <v>35795.4</v>
@@ -5095,9 +5095,9 @@
         <v>605915.5</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B55" s="5">
         <v>105055.9</v>
@@ -5172,9 +5172,9 @@
         <v>2672241.7999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B56" s="5">
         <v>76343.3</v>
@@ -5249,9 +5249,9 @@
         <v>1763998.8</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B57" s="5">
         <v>25218.7</v>
@@ -5326,9 +5326,9 @@
         <v>659002.80000000005</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B58" s="5">
         <v>140407.4</v>
@@ -5403,9 +5403,9 @@
         <v>2646488.2000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B59" s="5">
         <v>63068.2</v>
@@ -5480,9 +5480,9 @@
         <v>1345119</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B60" s="5">
         <v>30415</v>
@@ -5557,9 +5557,9 @@
         <v>673635.5</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B61" s="5">
         <v>18705.2</v>
@@ -5634,9 +5634,9 @@
         <v>380466.7</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B62" s="5">
         <v>156077</v>
@@ -5711,9 +5711,9 @@
         <v>4128119.1</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B63" s="5">
         <v>570790.19999999995</v>
@@ -5788,9 +5788,9 @@
         <v>15946597.199999999</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="31" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B64" s="5">
         <v>403822.2</v>
@@ -5865,9 +5865,9 @@
         <v>8628903.5</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B65" s="5">
         <v>117100.8</v>
@@ -5942,42 +5942,42 @@
         <v>5379401.7999999998</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="63" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="62" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M66" s="5">
         <v>706053</v>
@@ -6019,9 +6019,9 @@
         <v>1938291.9</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B67" s="5">
         <v>120561</v>
@@ -6096,9 +6096,9 @@
         <v>2589084.6</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B68" s="5">
         <v>2737.5</v>
@@ -6173,9 +6173,9 @@
         <v>108336.5</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B69" s="5">
         <v>3594.1</v>
@@ -6250,9 +6250,9 @@
         <v>122532.5</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B70" s="5">
         <v>17418.099999999999</v>
@@ -6327,9 +6327,9 @@
         <v>378551.6</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B71" s="5">
         <v>46736.800000000003</v>
@@ -6404,9 +6404,9 @@
         <v>1024355.4</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B72" s="5">
         <v>214662.7</v>
@@ -6481,9 +6481,9 @@
         <v>3719646.8</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B73" s="5">
         <v>103013.8</v>
@@ -6558,9 +6558,9 @@
         <v>2539383.9</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B74" s="5">
         <v>88728.1</v>
@@ -6635,9 +6635,9 @@
         <v>1883825.1</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B75" s="5">
         <v>72012.7</v>
@@ -6712,9 +6712,9 @@
         <v>2216436.2000000002</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B76" s="5">
         <v>46028.4</v>
@@ -6789,9 +6789,9 @@
         <v>1056600.3</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B77" s="5">
         <v>40539.5</v>
@@ -6866,9 +6866,9 @@
         <v>912449.4</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B78" s="5">
         <v>21574.5</v>
@@ -6943,9 +6943,9 @@
         <v>503918.8</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B79" s="5">
         <v>81960.399999999994</v>
@@ -7020,9 +7020,9 @@
         <v>2229816.5</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B80" s="5">
         <v>30024.6</v>
@@ -7097,9 +7097,9 @@
         <v>718358.3</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B81" s="5">
         <v>18140.7</v>
@@ -7174,9 +7174,9 @@
         <v>440147.3</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B82" s="5">
         <v>62088.5</v>
@@ -7251,9 +7251,9 @@
         <v>1862934.3</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B83" s="5">
         <v>64794.8</v>
@@ -7328,9 +7328,9 @@
         <v>1262368.1000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B84" s="5">
         <v>26315.200000000001</v>
@@ -7405,9 +7405,9 @@
         <v>793851.9</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B85" s="5">
         <v>13009.5</v>
@@ -7482,9 +7482,9 @@
         <v>403892.80000000005</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B86" s="5">
         <v>34777</v>
@@ -7559,9 +7559,9 @@
         <v>1624560.7</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="31" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B87" s="5">
         <v>3784</v>
@@ -7636,9 +7636,9 @@
         <v>102215.3</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="31" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B88" s="6">
         <v>3931.4</v>
